--- a/output/pdf_financials_xlsx/BBD.B.xlsx
+++ b/output/pdf_financials_xlsx/BBD.B.xlsx
@@ -5923,19 +5923,19 @@
         <v>-51</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>-5421</v>
+        <v>-5209</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>-1058</v>
+        <v>-1059</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-1903</v>
+        <v>-1849</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-1599</v>
+        <v>-1472</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-1167</v>
+        <v>-1086</v>
       </c>
     </row>
     <row r="125">
@@ -5967,19 +5967,19 @@
         <v>-51</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-5421</v>
+        <v>-5209</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-1058</v>
+        <v>-1059</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-1903</v>
+        <v>-1849</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-1599</v>
+        <v>-1472</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-1167</v>
+        <v>-1086</v>
       </c>
     </row>
     <row r="126">
